--- a/outputs/worship_planning_2026-02-01_2026-07-26.xlsx
+++ b/outputs/worship_planning_2026-02-01_2026-07-26.xlsx
@@ -423,17 +423,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Fecha Ensayo (Sábado)</t>
+          <t>Rehearsal Date (Saturday)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Fecha Presentación (Domingo)</t>
+          <t>Service Date (Sunday)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Horario Tentativo de Ensayo</t>
+          <t>Tentative Rehearsal Time</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -443,32 +443,32 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Guitarrista</t>
+          <t>Guitarist</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Baterista</t>
+          <t>Drummer</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Bajista</t>
+          <t>Bassist</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Tecladista</t>
+          <t>Keyboardist</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Corista_1</t>
+          <t>Vocalist_1</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Corista_2</t>
+          <t>Vocalist_2</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sábado en la tarde</t>
+          <t>Saturday afternoon</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sábado en la mañana</t>
+          <t>Saturday morning</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sábado en la tarde</t>
+          <t>Saturday afternoon</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sábado en la mañana</t>
+          <t>Saturday morning</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sábado en la tarde</t>
+          <t>Saturday afternoon</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sábado en la mañana</t>
+          <t>Saturday morning</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sábado en la tarde</t>
+          <t>Saturday afternoon</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sábado en la tarde</t>
+          <t>Saturday afternoon</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sábado en la mañana</t>
+          <t>Saturday morning</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sábado en la tarde</t>
+          <t>Saturday afternoon</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sábado en la mañana</t>
+          <t>Saturday morning</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sábado en la tarde</t>
+          <t>Saturday afternoon</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sábado en la mañana</t>
+          <t>Saturday morning</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sábado en la tarde</t>
+          <t>Saturday afternoon</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sábado en la mañana</t>
+          <t>Saturday morning</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sábado en la tarde</t>
+          <t>Saturday afternoon</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sábado en la mañana</t>
+          <t>Saturday morning</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sábado en la tarde</t>
+          <t>Saturday afternoon</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sábado en la mañana</t>
+          <t>Saturday morning</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sábado en la tarde</t>
+          <t>Saturday afternoon</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sábado en la tarde</t>
+          <t>Saturday afternoon</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sábado en la mañana</t>
+          <t>Saturday morning</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sábado en la tarde</t>
+          <t>Saturday afternoon</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sábado en la mañana</t>
+          <t>Saturday morning</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sábado en la tarde</t>
+          <t>Saturday afternoon</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sábado en la mañana</t>
+          <t>Saturday morning</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
